--- a/data/trans_orig/IP31KM03_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM03_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>102461</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>94482</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>108651</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>77,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>89,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>86887</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>79594</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>91943</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>85,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>78,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>90,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>114316</t>
+          <t>85384</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106425</t>
+          <t>78553</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121164</t>
+          <t>90430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>201203</t>
+          <t>187845</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>191175</t>
+          <t>178580</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209816</t>
+          <t>196421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18748</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12558</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26727</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>14822</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9766</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22115</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14,57%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>21,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28751</t>
+          <t>21796</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>35683</t>
+          <t>33713</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27070</t>
+          <t>25137</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45711</t>
+          <t>42978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>72785</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64707</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>78655</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>80,98%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>71,99%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>87,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>76176</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>69242</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>81691</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>81,57%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>74,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>87,47%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76061</t>
+          <t>77882</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67409</t>
+          <t>70958</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82201</t>
+          <t>83555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>152238</t>
+          <t>150667</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141689</t>
+          <t>140211</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160436</t>
+          <t>159973</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17095</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11225</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25173</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19,02%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>28,01%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>17216</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11701</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24150</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>17528</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>24452</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>34863</t>
+          <t>34623</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26665</t>
+          <t>25317</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45412</t>
+          <t>45079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>48527</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>43466</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>51836</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>86,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>77,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>92,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>44874</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39996</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>47917</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>89,59%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>79,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54271</t>
+          <t>46636</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49268</t>
+          <t>41773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58077</t>
+          <t>49797</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>99145</t>
+          <t>95163</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92078</t>
+          <t>88377</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103802</t>
+          <t>100093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7317</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4008</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12378</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5215</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2172</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10093</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10,41%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>164392</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>153620</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>173242</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>184242</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>173267</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>195168</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>85,48%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>80,39%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>90,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>176861</t>
+          <t>148261</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>165017</t>
+          <t>139557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186653</t>
+          <t>155778</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>361103</t>
+          <t>312653</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>344675</t>
+          <t>297804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>376254</t>
+          <t>324138</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>32921</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24071</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43693</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>22,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>31295</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20369</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>42270</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14,52%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>35797</t>
+          <t>28379</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47641</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>67093</t>
+          <t>61300</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51942</t>
+          <t>49815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83521</t>
+          <t>76149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>126319</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>117842</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>133185</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>86,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>80,94%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>91,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>96090</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>88599</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>102439</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>76,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>88,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>139360</t>
+          <t>95205</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>87914</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145979</t>
+          <t>101448</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>235450</t>
+          <t>221524</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>223733</t>
+          <t>209877</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245352</t>
+          <t>232183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19267</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>27744</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>13,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>19,06%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>19419</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13070</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26910</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>23,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20101</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>27552</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>39520</t>
+          <t>39528</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29618</t>
+          <t>28869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>51175</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>50313</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>43307</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>56072</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>76,39%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>65,75%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>85,13%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>58784</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>52992</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>62794</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>85,32%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>76,92%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>91,14%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53270</t>
+          <t>59824</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46195</t>
+          <t>53296</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58815</t>
+          <t>64478</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>112053</t>
+          <t>110138</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103108</t>
+          <t>100220</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120013</t>
+          <t>117795</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>15550</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9791</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>22556</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>23,61%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>34,25%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>10111</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6101</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>15903</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>8,86%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>23,08%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15761</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>17060</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>25872</t>
+          <t>26082</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>18425</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34817</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>564798</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>545337</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>580834</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>83,59%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>80,71%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>85,96%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>759</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>547052</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>529350</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>564817</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>84,8%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>82,05%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>87,55%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>614139</t>
+          <t>513193</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>594234</t>
+          <t>497704</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>632027</t>
+          <t>529152</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1161191</t>
+          <t>1077991</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1134372</t>
+          <t>1051172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1186824</t>
+          <t>1101337</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>110897</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>94861</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>130358</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>16,41%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>19,29%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>98079</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>80314</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>115781</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>17,95%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>118229</t>
+          <t>97039</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100341</t>
+          <t>81080</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>138134</t>
+          <t>112528</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>216308</t>
+          <t>207936</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>190675</t>
+          <t>184590</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>243127</t>
+          <t>234755</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
